--- a/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>PSQH</t>
   </si>
@@ -656,46 +656,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
-      </c>
-      <c r="G7" s="2">
-        <v>44834</v>
       </c>
       <c r="H7" s="2">
         <v>44742</v>
@@ -703,63 +705,69 @@
       <c r="I7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>2000</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
+      <c r="D9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>400</v>
+      </c>
+      <c r="F9" s="3">
+        <v>400</v>
+      </c>
+      <c r="G9" s="3">
+        <v>700</v>
+      </c>
+      <c r="H9" s="3">
+        <v>200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>100</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>4</v>
@@ -767,28 +775,31 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-100</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>4</v>
@@ -796,8 +807,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,28 +823,29 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
+      <c r="D12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>300</v>
+      </c>
+      <c r="F12" s="3">
+        <v>200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H12" s="3">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3">
+        <v>200</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
@@ -838,8 +853,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,66 +885,75 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>3300</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +962,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2800</v>
+        <v>15000</v>
       </c>
       <c r="E17" s="3">
-        <v>1500</v>
+        <v>7700</v>
       </c>
       <c r="F17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G17" s="3">
+        <v>7600</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="G17" s="3">
-        <v>200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>200</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="J17" s="3">
-        <v>400</v>
-      </c>
-      <c r="K17" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-13000</v>
       </c>
       <c r="E18" s="3">
-        <v>-1500</v>
+        <v>-7200</v>
       </c>
       <c r="F18" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-300</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,57 +1040,61 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>-7200</v>
       </c>
       <c r="E20" s="3">
-        <v>300</v>
+        <v>-13300</v>
       </c>
       <c r="F20" s="3">
-        <v>1700</v>
+        <v>-1200</v>
       </c>
       <c r="G20" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>2900</v>
-      </c>
-      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-19500</v>
       </c>
       <c r="E21" s="3">
-        <v>-1200</v>
+        <v>-19900</v>
       </c>
       <c r="F21" s="3">
-        <v>1300</v>
+        <v>-6100</v>
       </c>
       <c r="G21" s="3">
-        <v>500</v>
+        <v>-6100</v>
       </c>
       <c r="H21" s="3">
-        <v>2000</v>
+        <v>-1400</v>
       </c>
       <c r="I21" s="3">
-        <v>2600</v>
+        <v>-900</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>4</v>
@@ -1064,22 +1102,25 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1087,63 +1128,69 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-7100</v>
+        <v>-20200</v>
       </c>
       <c r="E23" s="3">
-        <v>-1200</v>
+        <v>-20700</v>
       </c>
       <c r="F23" s="3">
-        <v>1300</v>
+        <v>-6700</v>
       </c>
       <c r="G23" s="3">
-        <v>500</v>
+        <v>-7000</v>
       </c>
       <c r="H23" s="3">
-        <v>2000</v>
+        <v>-1600</v>
       </c>
       <c r="I23" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
+        <v>-1000</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>4</v>
@@ -1151,8 +1198,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1230,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-7600</v>
+        <v>-20200</v>
       </c>
       <c r="E26" s="3">
-        <v>-1700</v>
+        <v>-20700</v>
       </c>
       <c r="F26" s="3">
-        <v>900</v>
+        <v>-6700</v>
       </c>
       <c r="G26" s="3">
-        <v>400</v>
+        <v>-7000</v>
       </c>
       <c r="H26" s="3">
-        <v>1900</v>
+        <v>-1600</v>
       </c>
       <c r="I26" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
+        <v>-1000</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-7600</v>
+        <v>-20200</v>
       </c>
       <c r="E27" s="3">
-        <v>-1700</v>
+        <v>-20700</v>
       </c>
       <c r="F27" s="3">
-        <v>900</v>
+        <v>-6700</v>
       </c>
       <c r="G27" s="3">
-        <v>400</v>
+        <v>-7000</v>
       </c>
       <c r="H27" s="3">
-        <v>1900</v>
+        <v>-1600</v>
       </c>
       <c r="I27" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
+        <v>-1000</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,8 +1326,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1296,8 +1358,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1390,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1422,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>7200</v>
       </c>
       <c r="E32" s="3">
-        <v>-300</v>
+        <v>13300</v>
       </c>
       <c r="F32" s="3">
-        <v>-1700</v>
+        <v>1200</v>
       </c>
       <c r="G32" s="3">
-        <v>-700</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>-2200</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-7600</v>
+        <v>-20200</v>
       </c>
       <c r="E33" s="3">
-        <v>-1700</v>
+        <v>-20700</v>
       </c>
       <c r="F33" s="3">
-        <v>900</v>
+        <v>-6700</v>
       </c>
       <c r="G33" s="3">
-        <v>400</v>
+        <v>-7000</v>
       </c>
       <c r="H33" s="3">
-        <v>1900</v>
+        <v>-1600</v>
       </c>
       <c r="I33" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
+        <v>-1000</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,56 +1518,62 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-7600</v>
+        <v>-20200</v>
       </c>
       <c r="E35" s="3">
-        <v>-1700</v>
+        <v>-20700</v>
       </c>
       <c r="F35" s="3">
-        <v>900</v>
+        <v>-6700</v>
       </c>
       <c r="G35" s="3">
-        <v>400</v>
+        <v>-7000</v>
       </c>
       <c r="H35" s="3">
-        <v>1900</v>
+        <v>-1600</v>
       </c>
       <c r="I35" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
+        <v>-1000</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
-      </c>
-      <c r="G38" s="2">
-        <v>44834</v>
       </c>
       <c r="H38" s="2">
         <v>44742</v>
@@ -1498,14 +1581,17 @@
       <c r="I38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1603,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,269 +1617,297 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1200</v>
+        <v>25300</v>
       </c>
       <c r="E41" s="3">
-        <v>1800</v>
+        <v>6200</v>
       </c>
       <c r="F41" s="3">
-        <v>200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>300</v>
-      </c>
-      <c r="H41" s="3">
-        <v>300</v>
-      </c>
-      <c r="I41" s="3">
-        <v>500</v>
-      </c>
-      <c r="J41" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>10000</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="F45" s="3">
-        <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
-      </c>
-      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
-        <v>400</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1200</v>
+        <v>30300</v>
       </c>
       <c r="E46" s="3">
-        <v>1900</v>
+        <v>17300</v>
       </c>
       <c r="F46" s="3">
-        <v>400</v>
-      </c>
-      <c r="G46" s="3">
-        <v>600</v>
-      </c>
-      <c r="H46" s="3">
-        <v>700</v>
-      </c>
-      <c r="I46" s="3">
-        <v>900</v>
-      </c>
-      <c r="J46" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>1300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>175900</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>174400</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>174900</v>
+        <v>0</v>
       </c>
       <c r="G47" s="3">
-        <v>173500</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>172700</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="K47" s="3">
         <v>172500</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>172500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>2800</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1935,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +1967,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2031,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>177100</v>
+        <v>33200</v>
       </c>
       <c r="E54" s="3">
-        <v>176300</v>
+        <v>20100</v>
       </c>
       <c r="F54" s="3">
-        <v>175300</v>
-      </c>
-      <c r="G54" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
+        <v>173900</v>
+      </c>
+      <c r="L54" s="3">
         <v>174100</v>
       </c>
-      <c r="H54" s="3">
-        <v>173500</v>
-      </c>
-      <c r="I54" s="3">
-        <v>173500</v>
-      </c>
-      <c r="J54" s="3">
-        <v>173900</v>
-      </c>
-      <c r="K54" s="3">
-        <v>174100</v>
-      </c>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2079,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,37 +2093,41 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+        <v>1900</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2020,66 +2155,75 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4400</v>
+        <v>1500</v>
       </c>
       <c r="E59" s="3">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="F59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G59" s="3">
+        <v>900</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
-        <v>300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>300</v>
-      </c>
-      <c r="J59" s="3">
-        <v>500</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4400</v>
+        <v>3200</v>
       </c>
       <c r="E60" s="3">
-        <v>2300</v>
+        <v>3000</v>
       </c>
       <c r="F60" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>500</v>
       </c>
-      <c r="H60" s="3">
-        <v>300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>500</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2087,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>37100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2107,37 +2251,43 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>14900</v>
+        <v>18500</v>
       </c>
       <c r="E62" s="3">
-        <v>8600</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>7100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>7300</v>
-      </c>
-      <c r="H62" s="3">
-        <v>7300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J62" s="3">
+        <v>100</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>12100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2315,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2347,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2379,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>19300</v>
+        <v>21700</v>
       </c>
       <c r="E66" s="3">
-        <v>10800</v>
+        <v>40200</v>
       </c>
       <c r="F66" s="3">
-        <v>8200</v>
-      </c>
-      <c r="G66" s="3">
-        <v>7800</v>
-      </c>
-      <c r="H66" s="3">
-        <v>7600</v>
-      </c>
-      <c r="I66" s="3">
-        <v>9500</v>
-      </c>
-      <c r="J66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>12600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2427,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2457,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2489,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2521,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2553,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-17000</v>
+        <v>-56500</v>
       </c>
       <c r="E72" s="3">
-        <v>-7900</v>
+        <v>-36300</v>
       </c>
       <c r="F72" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-6800</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="J72" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>-11200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2617,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2649,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2681,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>157900</v>
+        <v>11500</v>
       </c>
       <c r="E76" s="3">
-        <v>165500</v>
+        <v>-20100</v>
       </c>
       <c r="F76" s="3">
-        <v>167100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>166200</v>
-      </c>
-      <c r="H76" s="3">
-        <v>165900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>163900</v>
-      </c>
-      <c r="J76" s="3">
+        <v>600</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>161300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,27 +2745,30 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
-      </c>
-      <c r="G80" s="2">
-        <v>44834</v>
       </c>
       <c r="H80" s="2">
         <v>44742</v>
@@ -2583,43 +2776,49 @@
       <c r="I80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="J80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-7600</v>
+        <v>-20200</v>
       </c>
       <c r="E81" s="3">
-        <v>-1700</v>
+        <v>-20700</v>
       </c>
       <c r="F81" s="3">
-        <v>900</v>
+        <v>-6700</v>
       </c>
       <c r="G81" s="3">
-        <v>400</v>
+        <v>-7000</v>
       </c>
       <c r="H81" s="3">
-        <v>1900</v>
+        <v>-1600</v>
       </c>
       <c r="I81" s="3">
-        <v>2600</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0</v>
+        <v>-1000</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +2830,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2892,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2924,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2956,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +2988,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3020,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1200</v>
+        <v>-2300</v>
       </c>
       <c r="E89" s="3">
-        <v>-800</v>
+        <v>-7000</v>
       </c>
       <c r="F89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,25 +3068,26 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -2876,8 +3098,11 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3130,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3162,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>600</v>
+        <v>9400</v>
       </c>
       <c r="E94" s="3">
-        <v>2400</v>
+        <v>-10500</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>-1600</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-22500</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,8 +3210,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3005,8 +3240,11 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3272,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3304,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +3336,43 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>4</v>
+      <c r="D100" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>20400</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+        <v>800</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3150,33 +3400,39 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-600</v>
+        <v>19100</v>
       </c>
       <c r="E102" s="3">
-        <v>1600</v>
+        <v>3000</v>
       </c>
       <c r="F102" s="3">
-        <v>-100</v>
+        <v>800</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="H102" s="3">
         <v>-200</v>
       </c>
       <c r="I102" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>PSQH</t>
   </si>
@@ -656,162 +656,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F8" s="3">
         <v>2000</v>
-      </c>
-      <c r="E8" s="3">
-        <v>500</v>
-      </c>
-      <c r="F8" s="3">
-        <v>400</v>
       </c>
       <c r="G8" s="3">
         <v>500</v>
       </c>
       <c r="H8" s="3">
+        <v>400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>500</v>
+      </c>
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F9" s="3">
         <v>1500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="3">
         <v>500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
         <v>-200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-100</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,40 +849,48 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F12" s="3">
         <v>1500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,20 +921,26 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F14" s="3">
         <v>3300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
@@ -914,46 +953,58 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>400</v>
+      </c>
+      <c r="F15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -963,72 +1014,86 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>16400</v>
+      </c>
+      <c r="F17" s="3">
         <v>15000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>7600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1000</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-13000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-7200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-5500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-7100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1041,136 +1106,162 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-7200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-13300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-19500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-19900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-6100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-6100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-900</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-20200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-20700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-6700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-7000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1000</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1192,17 +1283,23 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1233,72 +1330,90 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-20200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-20700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-6700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-7000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-20200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-20700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-6700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-7000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1329,8 +1444,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1361,8 +1482,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1393,8 +1520,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1425,72 +1558,90 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F32" s="3">
         <v>7200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>13300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-20200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-20700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-6700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-7000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1521,77 +1672,95 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-20200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-20700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-6700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-7000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1604,8 +1773,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1618,55 +1789,63 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>16400</v>
+      </c>
+      <c r="F41" s="3">
         <v>25300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3200</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" s="3">
         <v>10000</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>4</v>
       </c>
@@ -1676,26 +1855,32 @@
       <c r="J42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>200</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1708,26 +1893,32 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F44" s="3">
         <v>1500</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
@@ -1740,127 +1931,151 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F45" s="3">
         <v>3500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>21200</v>
+      </c>
+      <c r="F46" s="3">
         <v>30300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>17300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3600</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
         <v>1300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>172500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>172500</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="E48" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
+      <c r="G48" s="3">
+        <v>300</v>
+      </c>
+      <c r="H48" s="3">
+        <v>300</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>4</v>
@@ -1868,46 +2083,58 @@
       <c r="J48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F49" s="3">
         <v>2500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2800</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1938,8 +2165,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1970,25 +2203,31 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
       <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>4</v>
@@ -1996,14 +2235,20 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2034,40 +2279,52 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>25200</v>
+      </c>
+      <c r="F54" s="3">
         <v>33200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>20100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6700</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
         <v>173900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2080,8 +2337,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2094,63 +2353,71 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>5100</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2158,8 +2425,14 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2167,81 +2440,93 @@
         <v>1500</v>
       </c>
       <c r="E59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G59" s="3">
         <v>2500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F60" s="3">
         <v>3200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
         <v>500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>37100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3200</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2254,40 +2539,52 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F62" s="3">
         <v>18500</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>12100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2318,8 +2615,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2350,8 +2653,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2382,40 +2691,52 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F66" s="3">
         <v>21700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>40200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6100</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
         <v>12600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2428,8 +2749,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2460,8 +2783,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2492,8 +2821,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2524,8 +2859,14 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2556,40 +2897,52 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-74800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-62200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-56500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-36300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-15600</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
         <v>-11200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2620,8 +2973,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2652,8 +3011,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2684,40 +3049,52 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F76" s="3">
         <v>11500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-20100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>600</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
         <v>161300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2748,77 +3125,95 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-20200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-20700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-6700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-7000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2831,40 +3226,48 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>400</v>
+      </c>
+      <c r="F83" s="3">
         <v>800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2895,8 +3298,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2927,8 +3336,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2959,8 +3374,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2991,8 +3412,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3023,40 +3450,52 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-7000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-6000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3069,8 +3508,10 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3078,31 +3519,37 @@
         <v>-800</v>
       </c>
       <c r="E91" s="3">
-        <v>-400</v>
+        <v>-1500</v>
       </c>
       <c r="F91" s="3">
         <v>-800</v>
       </c>
       <c r="G91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3133,8 +3580,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3165,40 +3618,52 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F94" s="3">
         <v>9400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-10500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-22500</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3211,8 +3676,10 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3243,8 +3710,14 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3275,8 +3748,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3307,8 +3786,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3339,40 +3824,52 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F100" s="3">
         <v>12000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>20400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>4700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>9500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>800</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3403,36 +3900,48 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F102" s="3">
         <v>19100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
   <si>
     <t>PSQH</t>
   </si>
@@ -656,111 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="M7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -768,66 +775,69 @@
         <v>2000</v>
       </c>
       <c r="E9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1500</v>
-      </c>
-      <c r="G9" s="3">
-        <v>400</v>
       </c>
       <c r="H9" s="3">
         <v>400</v>
       </c>
       <c r="I9" s="3">
+        <v>400</v>
+      </c>
+      <c r="J9" s="3">
         <v>700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
       <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>-200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>-100</v>
       </c>
       <c r="K10" s="3">
         <v>-100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
+      <c r="L10" s="3">
+        <v>-100</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
@@ -835,8 +845,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,46 +864,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,23 +944,26 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>-200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
@@ -959,52 +979,58 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>900</v>
+      </c>
+      <c r="E15" s="3">
         <v>300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1042,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E17" s="3">
         <v>18400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,84 +1141,91 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E20" s="3">
         <v>2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-13300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-12300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-19500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-19900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-6100</v>
       </c>
       <c r="I21" s="3">
         <v>-6100</v>
       </c>
       <c r="J21" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1198,70 +1238,76 @@
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-20200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-20700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0</v>
+      <c r="M23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1289,8 +1335,8 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>4</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>4</v>
@@ -1298,8 +1344,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1385,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-20200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M26" s="3">
-        <v>0</v>
+      <c r="M26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-20200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0</v>
+      <c r="M27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1508,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1549,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1590,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,84 +1631,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>13300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-20200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M33" s="3">
-        <v>0</v>
+      <c r="M33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1754,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-20200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M35" s="3">
-        <v>0</v>
+      <c r="M35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M38" s="2">
+      <c r="M38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1860,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,29 +1877,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E41" s="3">
         <v>9100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3200</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1823,14 +1910,17 @@
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1843,12 +1933,12 @@
       <c r="F42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H42" s="3">
         <v>10000</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>4</v>
       </c>
@@ -1861,29 +1951,32 @@
       <c r="L42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1899,29 +1992,32 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1500</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
@@ -1937,35 +2033,38 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E45" s="3">
         <v>3200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
@@ -1975,35 +2074,38 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E46" s="3">
         <v>19800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>21200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>30300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3600</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2013,23 +2115,26 @@
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>1300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>600</v>
+      </c>
+      <c r="E47" s="3">
         <v>1100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>4</v>
       </c>
@@ -2045,31 +2150,34 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="N47" s="3">
         <v>172500</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>172500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>800</v>
+      </c>
+      <c r="E48" s="3">
         <v>900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>300</v>
@@ -2077,8 +2185,8 @@
       <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
+      <c r="I48" s="3">
+        <v>300</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>4</v>
@@ -2089,35 +2197,38 @@
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E49" s="3">
         <v>26700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2800</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2127,14 +2238,17 @@
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2285,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,8 +2326,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2218,19 +2338,19 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>4</v>
+      <c r="I52" s="3">
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>4</v>
@@ -2241,14 +2361,17 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,29 +2408,32 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E54" s="3">
         <v>48600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6700</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2317,14 +2443,17 @@
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>173900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2468,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,29 +2485,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>6600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1900</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2387,23 +2518,26 @@
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E58" s="3">
         <v>5100</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2419,8 +2553,8 @@
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2431,29 +2565,32 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
@@ -2463,35 +2600,38 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E60" s="3">
         <v>13200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2800</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2501,35 +2641,38 @@
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E61" s="3">
         <v>8400</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>37100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3200</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2545,29 +2688,32 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E62" s="3">
         <v>8700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18500</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
@@ -2577,14 +2723,17 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>12100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2770,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2811,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,29 +2852,32 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E66" s="3">
         <v>30300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>40200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6100</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>4</v>
       </c>
@@ -2729,14 +2887,17 @@
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>12600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +2912,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +2951,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +2992,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3033,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,29 +3074,32 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-74800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-62200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-56500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-36300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-15600</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>4</v>
       </c>
@@ -2935,14 +3109,17 @@
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>-11200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3156,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3197,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,29 +3238,32 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E76" s="3">
         <v>18300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-20100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>600</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3087,14 +3273,17 @@
       <c r="L76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N76" s="3">
         <v>161300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3320,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M80" s="2">
+      <c r="M80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-20200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M81" s="3">
-        <v>0</v>
+      <c r="M81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,46 +3426,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3506,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3547,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3588,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3629,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +3670,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,35 +3730,36 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-800</v>
       </c>
       <c r="I91" s="3">
         <v>-800</v>
       </c>
       <c r="J91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -3548,8 +3769,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +3810,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +3851,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>9400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-22500</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,8 +3911,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3716,8 +3950,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +3991,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4032,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,46 +4073,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>20400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>9500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3906,42 +4155,48 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1900</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-200</v>
       </c>
       <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="L102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
   <si>
     <t>PSQH</t>
   </si>
@@ -656,191 +656,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N7" s="2">
+      <c r="N7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E8" s="3">
         <v>6000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="E9" s="3">
         <v>2000</v>
       </c>
       <c r="F9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="3">
         <v>1700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>400</v>
       </c>
       <c r="I9" s="3">
         <v>400</v>
       </c>
       <c r="J9" s="3">
+        <v>400</v>
+      </c>
+      <c r="K9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E10" s="3">
         <v>4000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1000</v>
       </c>
-      <c r="G10" s="3">
-        <v>500</v>
-      </c>
       <c r="H10" s="3">
+        <v>600</v>
+      </c>
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
         <v>-200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>-100</v>
       </c>
       <c r="L10" s="3">
         <v>-100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
+      <c r="M10" s="3">
+        <v>-100</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>4</v>
@@ -848,8 +858,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +878,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -874,40 +888,43 @@
         <v>1000</v>
       </c>
       <c r="E12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="3">
         <v>1100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,31 +964,34 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2100</v>
       </c>
       <c r="F14" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="G14" s="3">
-        <v>3300</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
+        <v>-1500</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I14" s="3">
+        <v>13400</v>
+      </c>
+      <c r="J14" s="3">
+        <v>1100</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
@@ -982,55 +1002,61 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
         <v>900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,90 +1069,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20000</v>
+        <v>18900</v>
       </c>
       <c r="E17" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F17" s="3">
         <v>18400</v>
       </c>
-      <c r="F17" s="3">
-        <v>16400</v>
-      </c>
       <c r="G17" s="3">
-        <v>15000</v>
+        <v>16600</v>
       </c>
       <c r="H17" s="3">
+        <v>11700</v>
+      </c>
+      <c r="I17" s="3">
         <v>7700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-14000</v>
+        <v>-12400</v>
       </c>
       <c r="E18" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-14900</v>
       </c>
-      <c r="F18" s="3">
-        <v>-13700</v>
-      </c>
       <c r="G18" s="3">
-        <v>-13000</v>
+        <v>-13800</v>
       </c>
       <c r="H18" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-7200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,172 +1175,185 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2800</v>
+        <v>-2100</v>
       </c>
       <c r="E20" s="3">
-        <v>2300</v>
+        <v>-3100</v>
       </c>
       <c r="F20" s="3">
-        <v>8000</v>
+        <v>-2300</v>
       </c>
       <c r="G20" s="3">
-        <v>-7200</v>
+        <v>-6600</v>
       </c>
       <c r="H20" s="3">
-        <v>-13300</v>
+        <v>7700</v>
       </c>
       <c r="I20" s="3">
-        <v>-1200</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-10300</v>
+        <v>-9300</v>
       </c>
       <c r="E21" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-12300</v>
       </c>
-      <c r="F21" s="3">
-        <v>-5200</v>
-      </c>
       <c r="G21" s="3">
-        <v>-19500</v>
+        <v>-6800</v>
       </c>
       <c r="H21" s="3">
-        <v>-19900</v>
+        <v>-16600</v>
       </c>
       <c r="I21" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-6100</v>
       </c>
-      <c r="J21" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>600</v>
+      </c>
+      <c r="F22" s="3">
+        <v>100</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-20200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N23" s="3">
-        <v>0</v>
+      <c r="N23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1338,8 +1384,8 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>4</v>
@@ -1347,8 +1393,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,90 +1437,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N26" s="3">
-        <v>0</v>
+      <c r="N26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N27" s="3">
-        <v>0</v>
+      <c r="N27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1569,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1613,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1657,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,90 +1701,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2800</v>
+        <v>2100</v>
       </c>
       <c r="E32" s="3">
-        <v>-2300</v>
+        <v>3100</v>
       </c>
       <c r="F32" s="3">
-        <v>-8000</v>
+        <v>2300</v>
       </c>
       <c r="G32" s="3">
-        <v>7200</v>
+        <v>6600</v>
       </c>
       <c r="H32" s="3">
-        <v>13300</v>
+        <v>-7700</v>
       </c>
       <c r="I32" s="3">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N33" s="3">
-        <v>0</v>
+      <c r="N33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,95 +1833,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N35" s="3">
-        <v>0</v>
+      <c r="N35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N38" s="2">
+      <c r="N38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +1946,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,32 +1964,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E41" s="3">
         <v>7600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3200</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>4</v>
       </c>
@@ -1913,37 +2000,40 @@
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3">
         <v>800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>4</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>10000</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
@@ -1954,32 +2044,35 @@
       <c r="M42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E43" s="3">
         <v>5000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1995,32 +2088,35 @@
       <c r="M43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1500</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2036,37 +2132,40 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>2900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1000</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
+      <c r="J45" s="3">
+        <v>100</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>4</v>
@@ -2077,38 +2176,41 @@
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>30300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3600</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2118,22 +2220,25 @@
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O46" s="3">
         <v>1300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>600</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1100</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>4</v>
@@ -2153,34 +2258,37 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
       <c r="N47" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="O47" s="3">
         <v>172500</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>172500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
         <v>800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>300</v>
       </c>
       <c r="H48" s="3">
         <v>300</v>
@@ -2188,8 +2296,8 @@
       <c r="I48" s="3">
         <v>300</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
+      <c r="J48" s="3">
+        <v>300</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>4</v>
@@ -2200,38 +2308,41 @@
       <c r="M48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E49" s="3">
         <v>26800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2800</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2241,14 +2352,17 @@
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2402,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,31 +2446,34 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>4</v>
@@ -2364,14 +2484,17 @@
       <c r="M52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,32 +2534,35 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E54" s="3">
         <v>45100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>48600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6700</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2446,14 +2572,17 @@
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>173900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2598,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,32 +2616,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1900</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2521,43 +2652,46 @@
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="N57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3500</v>
+        <v>3300</v>
       </c>
       <c r="E58" s="3">
-        <v>5100</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
+        <v>3800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G58" s="3">
+        <v>300</v>
+      </c>
+      <c r="H58" s="3">
+        <v>200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>200</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2568,31 +2702,34 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="E59" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="F59" s="3">
-        <v>2200</v>
+        <v>100</v>
       </c>
       <c r="G59" s="3">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="H59" s="3">
-        <v>2500</v>
+        <v>200</v>
       </c>
       <c r="I59" s="3">
-        <v>900</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>100</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>4</v>
@@ -2603,38 +2740,41 @@
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E60" s="3">
         <v>9000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2800</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2644,37 +2784,40 @@
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18400</v>
+        <v>28600</v>
       </c>
       <c r="E61" s="3">
-        <v>8400</v>
+        <v>18700</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>37100</v>
       </c>
-      <c r="I61" s="3">
-        <v>3200</v>
-      </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2691,28 +2834,31 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5300</v>
+        <v>2800</v>
       </c>
       <c r="E62" s="3">
-        <v>8700</v>
+        <v>5100</v>
       </c>
       <c r="F62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G62" s="3">
         <v>10800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18500</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>100</v>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
@@ -2726,14 +2872,17 @@
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>12100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +2922,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +2966,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,32 +3010,35 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E66" s="3">
         <v>32800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>30300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>40200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>4</v>
       </c>
@@ -2890,14 +3048,17 @@
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>12600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3074,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3116,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3160,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3204,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,32 +3248,35 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-99200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-86000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-74800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-62200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-56500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-36300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-15600</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3112,14 +3286,17 @@
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O72" s="3">
         <v>-11200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3336,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3380,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,32 +3424,35 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E76" s="3">
         <v>12200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-20100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>600</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3276,14 +3462,17 @@
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>161300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,95 +3512,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="N80" s="2">
+      <c r="N80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N81" s="3">
-        <v>0</v>
+      <c r="N81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,49 +3625,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3">
         <v>800</v>
       </c>
-      <c r="H83" s="3">
-        <v>700</v>
-      </c>
-      <c r="I83" s="3">
-        <v>500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>800</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3711,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3755,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +3799,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +3843,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +3887,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6500</v>
       </c>
-      <c r="F89" s="3">
-        <v>-13500</v>
-      </c>
       <c r="G89" s="3">
-        <v>-2300</v>
+        <v>-7400</v>
       </c>
       <c r="H89" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="I89" s="3">
         <v>-7000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,38 +3951,39 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -3772,8 +3993,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4037,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,49 +4081,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E94" s="3">
         <v>400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>9400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-22500</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,31 +4145,32 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3953,8 +4187,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4231,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4275,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,72 +4319,78 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E100" s="3">
         <v>8400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
-        <v>6100</v>
-      </c>
       <c r="G100" s="3">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>18100</v>
+      </c>
+      <c r="I100" s="3">
         <v>20400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4158,45 +4407,51 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1900</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-200</v>
       </c>
       <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="M102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
   <si>
     <t>PSQH</t>
   </si>
@@ -656,204 +656,213 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="O7" s="2">
+      <c r="O7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E8" s="3">
         <v>6500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E9" s="3">
         <v>2400</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2000</v>
       </c>
       <c r="F9" s="3">
         <v>2000</v>
       </c>
       <c r="G9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H9" s="3">
         <v>1700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>400</v>
       </c>
       <c r="J9" s="3">
         <v>400</v>
       </c>
       <c r="K9" s="3">
+        <v>400</v>
+      </c>
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>100</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E10" s="3">
         <v>4200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
       <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>-200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>-100</v>
       </c>
       <c r="M10" s="3">
         <v>-100</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>4</v>
+      <c r="N10" s="3">
+        <v>-100</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>4</v>
@@ -861,8 +870,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -879,52 +891,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="E12" s="3">
         <v>1000</v>
       </c>
       <c r="F12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G12" s="3">
         <v>1100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,35 +983,38 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2100</v>
+        <v>-1800</v>
       </c>
       <c r="E14" s="3">
         <v>2100</v>
       </c>
       <c r="F14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1005,58 +1024,64 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E15" s="3">
         <v>1000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,96 +1095,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E17" s="3">
         <v>18900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-9700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1176,184 +1208,197 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7700</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-12300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>900</v>
+      </c>
+      <c r="E22" s="3">
         <v>800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-13100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-20700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O23" s="3">
-        <v>0</v>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1387,8 +1432,8 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>4</v>
@@ -1396,8 +1441,11 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1440,96 +1488,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-13100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O26" s="3">
-        <v>0</v>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-13100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O27" s="3">
-        <v>0</v>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1572,8 +1629,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1660,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1704,96 +1770,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E32" s="3">
         <v>2100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7700</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-13100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O33" s="3">
-        <v>0</v>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1836,101 +1911,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-13100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O35" s="3">
-        <v>0</v>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="O38" s="2">
+      <c r="O38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1947,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1965,35 +2050,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E41" s="3">
         <v>4700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2003,14 +2089,17 @@
       <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P41" s="3">
         <v>800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2030,13 +2119,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>10000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>4</v>
@@ -2047,35 +2136,38 @@
       <c r="N42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E43" s="3">
         <v>4500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2091,35 +2183,38 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1500</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2135,14 +2230,17 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2161,15 +2259,15 @@
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2179,41 +2277,44 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E46" s="3">
         <v>16000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>30300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3600</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2223,14 +2324,17 @@
       <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P46" s="3">
         <v>1300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2261,37 +2365,40 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
       <c r="O47" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="P47" s="3">
         <v>172500</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>172500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
         <v>700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>500</v>
-      </c>
-      <c r="H48" s="3">
-        <v>300</v>
       </c>
       <c r="I48" s="3">
         <v>300</v>
@@ -2299,8 +2406,8 @@
       <c r="J48" s="3">
         <v>300</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
+      <c r="K48" s="3">
+        <v>300</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
@@ -2311,41 +2418,44 @@
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E49" s="3">
         <v>26900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>26700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2800</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2355,14 +2465,17 @@
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2405,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2449,8 +2565,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2458,25 +2577,25 @@
         <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
@@ -2487,14 +2606,17 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2537,35 +2659,38 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E54" s="3">
         <v>44200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>48600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2575,14 +2700,17 @@
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P54" s="3">
         <v>173900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2599,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2617,35 +2746,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E57" s="3">
         <v>3700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2655,31 +2785,34 @@
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E58" s="3">
         <v>3300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
-      </c>
-      <c r="H58" s="3">
-        <v>200</v>
       </c>
       <c r="I58" s="3">
         <v>200</v>
@@ -2687,14 +2820,14 @@
       <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
+      <c r="K58" s="3">
+        <v>200</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2705,34 +2838,37 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>300</v>
+      </c>
+      <c r="E59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
+      <c r="K59" s="3">
+        <v>100</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
@@ -2743,41 +2879,44 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3">
         <v>500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E60" s="3">
         <v>8400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2800</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2787,14 +2926,17 @@
       <c r="N60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P60" s="3">
         <v>500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2802,26 +2944,26 @@
         <v>28600</v>
       </c>
       <c r="E61" s="3">
+        <v>28600</v>
+      </c>
+      <c r="F61" s="3">
         <v>18700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8700</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>37100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2837,29 +2979,32 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E62" s="3">
         <v>2800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18500</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
@@ -2875,14 +3020,17 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P62" s="3">
         <v>12100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2925,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2969,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3013,35 +3167,38 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E66" s="3">
         <v>39800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>21700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>40200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3051,14 +3208,17 @@
       <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P66" s="3">
         <v>12600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3075,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3119,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3163,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3207,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3251,35 +3421,38 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-119900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-99200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-86000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-74800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-62200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-56500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-36300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-15600</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3289,14 +3462,17 @@
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P72" s="3">
         <v>-11200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3339,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3383,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3427,35 +3609,38 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-20100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3465,14 +3650,17 @@
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P76" s="3">
         <v>161300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3515,101 +3703,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="O80" s="2">
+      <c r="O80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-13100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O81" s="3">
-        <v>0</v>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3626,8 +3823,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3641,37 +3839,40 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3714,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3758,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3802,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3846,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3890,52 +4103,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3952,8 +4171,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3966,27 +4186,27 @@
       <c r="F91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -3996,8 +4216,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4040,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4084,52 +4310,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>9400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-22500</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4146,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4172,8 +4405,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4190,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4234,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4278,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4322,52 +4564,58 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E100" s="3">
         <v>9100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>18100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>20400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4392,8 +4640,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4410,48 +4658,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1900</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-200</v>
       </c>
       <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="N102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
   <si>
     <t>PSQH</t>
   </si>
@@ -656,131 +656,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P7" s="2">
+      <c r="P7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E8" s="3">
         <v>7200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -788,84 +795,87 @@
         <v>2800</v>
       </c>
       <c r="E9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F9" s="3">
         <v>2400</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2000</v>
       </c>
       <c r="G9" s="3">
         <v>2000</v>
       </c>
       <c r="H9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1500</v>
-      </c>
-      <c r="J9" s="3">
-        <v>400</v>
       </c>
       <c r="K9" s="3">
         <v>400</v>
       </c>
       <c r="L9" s="3">
+        <v>400</v>
+      </c>
+      <c r="M9" s="3">
         <v>700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E10" s="3">
         <v>4400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
       <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
         <v>-200</v>
-      </c>
-      <c r="M10" s="3">
-        <v>-100</v>
       </c>
       <c r="N10" s="3">
         <v>-100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
+      <c r="O10" s="3">
+        <v>-100</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,55 +905,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1000</v>
       </c>
       <c r="F12" s="3">
         <v>1000</v>
       </c>
       <c r="G12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H12" s="3">
         <v>1100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,38 +1003,41 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1800</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2100</v>
       </c>
       <c r="F14" s="3">
         <v>2100</v>
       </c>
       <c r="G14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1027,61 +1047,67 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E15" s="3">
         <v>1100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>100</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1122,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E17" s="3">
         <v>21600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-9700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,102 +1242,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E20" s="3">
         <v>7300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-2300</v>
-      </c>
       <c r="H20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-6600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7700</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7700</v>
       </c>
-      <c r="G21" s="3">
-        <v>-12300</v>
-      </c>
       <c r="H21" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-6800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1312,93 +1352,99 @@
         <v>900</v>
       </c>
       <c r="E22" s="3">
+        <v>900</v>
+      </c>
+      <c r="F22" s="3">
         <v>800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-20700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-20200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-20700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P23" s="3">
-        <v>0</v>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1435,8 +1481,8 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>4</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>4</v>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1540,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-20700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-13100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-20700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P26" s="3">
-        <v>0</v>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-20700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-13100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P27" s="3">
-        <v>0</v>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,102 +1840,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3100</v>
       </c>
-      <c r="G32" s="3">
-        <v>2300</v>
-      </c>
       <c r="H32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I32" s="3">
         <v>6600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7700</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-20700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-13100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-20700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P33" s="3">
-        <v>0</v>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +1990,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-20700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-13100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-20700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P35" s="3">
-        <v>0</v>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P38" s="2">
+      <c r="P38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,38 +2137,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E41" s="3">
         <v>36300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2092,14 +2179,17 @@
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q41" s="3">
         <v>800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2122,13 +2212,13 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>10000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>4</v>
@@ -2139,38 +2229,41 @@
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E43" s="3">
         <v>4700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2186,38 +2279,41 @@
       <c r="O43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E44" s="3">
         <v>2700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1500</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2233,19 +2329,22 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>700</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>4</v>
@@ -2262,15 +2361,15 @@
       <c r="I45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2280,44 +2379,47 @@
       <c r="O45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E46" s="3">
         <v>46800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>30300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3600</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2327,14 +2429,17 @@
       <c r="O46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q46" s="3">
         <v>1300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2368,40 +2473,43 @@
       <c r="M47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
       <c r="P47" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="3">
         <v>172500</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>172500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>500</v>
+      </c>
+      <c r="E48" s="3">
         <v>600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>300</v>
       </c>
       <c r="J48" s="3">
         <v>300</v>
@@ -2409,8 +2517,8 @@
       <c r="K48" s="3">
         <v>300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
+      <c r="L48" s="3">
+        <v>300</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>4</v>
@@ -2421,44 +2529,47 @@
       <c r="O48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E49" s="3">
         <v>26700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>26800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>26700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2800</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2468,14 +2579,17 @@
       <c r="O49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,8 +2685,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2580,25 +2700,25 @@
         <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
@@ -2609,14 +2729,17 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,38 +2785,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E54" s="3">
         <v>74900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>44200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>33200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2703,14 +2829,17 @@
       <c r="O54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q54" s="3">
         <v>173900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,38 +2877,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E57" s="3">
         <v>3500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2788,34 +2919,37 @@
       <c r="O57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="P57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E58" s="3">
         <v>3900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>200</v>
       </c>
       <c r="J58" s="3">
         <v>200</v>
@@ -2823,14 +2957,14 @@
       <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
+      <c r="L58" s="3">
+        <v>200</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2841,37 +2975,40 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100</v>
+      </c>
+      <c r="E59" s="3">
         <v>300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>100</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
+      <c r="L59" s="3">
+        <v>100</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
@@ -2882,14 +3019,17 @@
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2897,29 +3037,29 @@
         <v>8600</v>
       </c>
       <c r="E60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F60" s="3">
         <v>8400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2800</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>4</v>
       </c>
@@ -2929,14 +3069,17 @@
       <c r="O60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q60" s="3">
         <v>500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2947,26 +3090,26 @@
         <v>28600</v>
       </c>
       <c r="F61" s="3">
+        <v>28600</v>
+      </c>
+      <c r="G61" s="3">
         <v>18700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8700</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>37100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2982,32 +3125,35 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E62" s="3">
         <v>10800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18500</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3023,14 +3169,17 @@
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3">
         <v>12100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,38 +3325,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E66" s="3">
         <v>48000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>21700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>40200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3211,14 +3369,17 @@
       <c r="O66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="3">
         <v>12600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,38 +3595,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-124300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-119900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-99200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-86000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-74800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-62200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-56500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-36300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-15600</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3465,14 +3639,17 @@
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,38 +3795,41 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E76" s="3">
         <v>26900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-20100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>600</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3653,14 +3839,17 @@
       <c r="O76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q76" s="3">
         <v>161300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +3895,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P80" s="2">
+      <c r="P80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-20700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-13100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-20700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P81" s="3">
-        <v>0</v>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4022,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3842,37 +4041,40 @@
         <v>0</v>
       </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3">
         <v>800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4320,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4392,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4189,27 +4410,27 @@
       <c r="G91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -4219,8 +4440,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,55 +4540,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>9400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-22500</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4408,8 +4642,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,55 +4810,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>40000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>18100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>20400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4643,8 +4892,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4661,51 +4910,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E102" s="3">
         <v>30900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1900</v>
-      </c>
-      <c r="M102" s="3">
-        <v>-200</v>
       </c>
       <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="O102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>PSQH</t>
   </si>
@@ -656,229 +656,239 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E8" s="3">
         <v>6700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2800</v>
+        <v>3400</v>
       </c>
       <c r="E9" s="3">
         <v>2800</v>
       </c>
       <c r="F9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G9" s="3">
         <v>2400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2000</v>
       </c>
       <c r="H9" s="3">
         <v>2000</v>
       </c>
       <c r="I9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J9" s="3">
         <v>1700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1500</v>
-      </c>
-      <c r="K9" s="3">
-        <v>400</v>
       </c>
       <c r="L9" s="3">
         <v>400</v>
       </c>
       <c r="M9" s="3">
+        <v>400</v>
+      </c>
+      <c r="N9" s="3">
         <v>700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E10" s="3">
         <v>3900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
       <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
         <v>-200</v>
-      </c>
-      <c r="N10" s="3">
-        <v>-100</v>
       </c>
       <c r="O10" s="3">
         <v>-100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>4</v>
+      <c r="P10" s="3">
+        <v>-100</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>4</v>
@@ -886,8 +896,11 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,58 +919,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E12" s="3">
         <v>1400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1300</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1000</v>
       </c>
       <c r="G12" s="3">
         <v>1000</v>
       </c>
       <c r="H12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="3">
         <v>1100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,41 +1023,44 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1800</v>
-      </c>
-      <c r="F14" s="3">
-        <v>2100</v>
       </c>
       <c r="G14" s="3">
         <v>2100</v>
       </c>
       <c r="H14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1050,64 +1070,70 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E15" s="3">
         <v>1200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>100</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1149,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E17" s="3">
         <v>18400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>21600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18900</v>
       </c>
-      <c r="G17" s="3">
-        <v>17700</v>
-      </c>
       <c r="H17" s="3">
+        <v>20000</v>
+      </c>
+      <c r="I17" s="3">
         <v>18400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-12400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-11700</v>
-      </c>
       <c r="H18" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-14900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,108 +1276,115 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>7700</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-20600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-7700</v>
-      </c>
       <c r="H21" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="I21" s="3">
         <v>-12400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1355,96 +1395,102 @@
         <v>900</v>
       </c>
       <c r="F22" s="3">
+        <v>900</v>
+      </c>
+      <c r="G22" s="3">
         <v>800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-20700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-13100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-20200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-20700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>0</v>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1484,8 +1530,8 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>4</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>4</v>
@@ -1493,8 +1539,11 @@
       <c r="R24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1592,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-20700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-20200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>0</v>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-20700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-13100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>0</v>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1751,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1804,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1857,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1910,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>7400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-7700</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-20700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-13100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-20200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-20700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>0</v>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2069,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-20700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-13100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-20200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-20700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>0</v>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2203,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,41 +2224,42 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E41" s="3">
         <v>28000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3200</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2182,14 +2269,17 @@
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="3">
         <v>800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2215,13 +2305,13 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>10000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>4</v>
@@ -2232,41 +2322,44 @@
       <c r="P42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E43" s="3">
         <v>4600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2282,41 +2375,44 @@
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E44" s="3">
         <v>2400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1500</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2332,23 +2428,26 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>800</v>
+      </c>
+      <c r="E45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2364,15 +2463,15 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2382,47 +2481,50 @@
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E46" s="3">
         <v>38700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>46800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>30300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3600</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2432,14 +2534,17 @@
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R46" s="3">
         <v>1300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2476,43 +2581,46 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
       <c r="Q47" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="R47" s="3">
         <v>172500</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>172500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
         <v>500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>500</v>
-      </c>
-      <c r="J48" s="3">
-        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>300</v>
@@ -2520,8 +2628,8 @@
       <c r="L48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
+      <c r="M48" s="3">
+        <v>300</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>4</v>
@@ -2532,47 +2640,50 @@
       <c r="P48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E49" s="3">
         <v>26300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>26900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>26800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>26700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2800</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2582,14 +2693,17 @@
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2752,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,8 +2805,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2703,25 +2823,25 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
@@ -2732,14 +2852,17 @@
       <c r="P52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,41 +2911,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E54" s="3">
         <v>66200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>74900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>44200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>45100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>48600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6700</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>4</v>
       </c>
@@ -2832,14 +2958,17 @@
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" s="3">
         <v>173900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2987,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,41 +3008,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E57" s="3">
         <v>3100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>4</v>
       </c>
@@ -2922,37 +3053,40 @@
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
@@ -2960,14 +3094,14 @@
       <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
+      <c r="M58" s="3">
+        <v>200</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2978,40 +3112,43 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>100</v>
       </c>
       <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
+      <c r="M59" s="3">
+        <v>100</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
@@ -3022,47 +3159,50 @@
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8600</v>
+        <v>10900</v>
       </c>
       <c r="E60" s="3">
         <v>8600</v>
       </c>
       <c r="F60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="G60" s="3">
         <v>8400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2800</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3072,19 +3212,22 @@
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3">
         <v>500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>28600</v>
+        <v>28800</v>
       </c>
       <c r="E61" s="3">
         <v>28600</v>
@@ -3093,26 +3236,26 @@
         <v>28600</v>
       </c>
       <c r="G61" s="3">
+        <v>28600</v>
+      </c>
+      <c r="H61" s="3">
         <v>18700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8700</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>37100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3128,35 +3271,38 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E62" s="3">
         <v>3000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3172,14 +3318,17 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3">
         <v>12100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3377,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3430,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,41 +3483,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E66" s="3">
         <v>40100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>48000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>30300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>21700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>40200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6100</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3372,14 +3530,17 @@
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" s="3">
         <v>12600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3559,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3610,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3663,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3716,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,41 +3769,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-132700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-124300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-119900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-99200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-86000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-74800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-62200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-56500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-36300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-15600</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3642,14 +3816,17 @@
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>-11200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3875,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3928,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,41 +3981,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E76" s="3">
         <v>26000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-20100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>600</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>4</v>
       </c>
@@ -3842,14 +4028,17 @@
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R76" s="3">
         <v>161300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4087,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q80" s="2">
+      <c r="Q80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-20700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-13100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-20200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-20700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>0</v>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4221,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4044,37 +4243,40 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4325,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4378,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4431,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4484,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4537,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4613,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4413,27 +4634,27 @@
       <c r="H91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -4443,8 +4664,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4717,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4770,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>9400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-22500</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4846,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4645,8 +4879,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4663,8 +4897,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4950,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5003,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,58 +5056,64 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>40000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>18100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>20400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4895,8 +5144,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4913,54 +5162,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>30900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1900</v>
-      </c>
-      <c r="N102" s="3">
-        <v>-200</v>
       </c>
       <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="P102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>PSQH</t>
   </si>
@@ -656,255 +656,264 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="S7" s="2">
+      <c r="S7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E8" s="3">
         <v>4400</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
         <v>6700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3200</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="3">
         <v>3500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1500</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2800</v>
+      <c r="F9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G9" s="3">
         <v>2800</v>
       </c>
       <c r="H9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="3">
         <v>2000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1500</v>
-      </c>
-      <c r="M9" s="3">
-        <v>400</v>
       </c>
       <c r="N9" s="3">
         <v>400</v>
       </c>
       <c r="O9" s="3">
+        <v>400</v>
+      </c>
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>100</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E10" s="3">
         <v>3000</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3">
         <v>3900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3100</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="3">
         <v>1500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
       <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
         <v>-200</v>
-      </c>
-      <c r="P10" s="3">
-        <v>-100</v>
       </c>
       <c r="Q10" s="3">
         <v>-100</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
+      <c r="R10" s="3">
+        <v>-100</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>4</v>
@@ -912,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>600</v>
+      </c>
+      <c r="E12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="3">
         <v>1400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="3">
         <v>1100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,47 +1062,50 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>-500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1096,70 +1115,76 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="E15" s="3">
         <v>1700</v>
       </c>
       <c r="F15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G15" s="3">
         <v>1200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>100</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E17" s="3">
         <v>14100</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="3">
         <v>18400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13500</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="3">
         <v>18400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1000</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9700</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="3">
         <v>-11700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-10300</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
         <v>-14900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,243 +1343,256 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3">
         <v>-7400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2200</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7700</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-20600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-12400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>900</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="E22" s="3">
         <v>900</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G22" s="3">
         <v>900</v>
       </c>
       <c r="H22" s="3">
+        <v>900</v>
+      </c>
+      <c r="I22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10100</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="3">
         <v>-4400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-20700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8700</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="3">
         <v>-12600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-20200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-20700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S23" s="3">
-        <v>0</v>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1555,11 +1600,11 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1582,8 +1627,8 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>4</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>4</v>
@@ -1591,8 +1636,11 @@
       <c r="T24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10000</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="3">
         <v>-4400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8600</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="3">
         <v>-12600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-20700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S26" s="3">
-        <v>0</v>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12000</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27" s="3">
         <v>-4400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13100</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="3">
         <v>-12600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S27" s="3">
-        <v>0</v>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,17 +1872,20 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1900</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -1833,11 +1893,11 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-4500</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
@@ -1871,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3">
         <v>7400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2200</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
         <v>2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7700</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12000</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="3">
         <v>-4400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13100</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="3">
         <v>-12600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S33" s="3">
-        <v>0</v>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12000</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="3">
         <v>-4400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13100</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
         <v>-12600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S35" s="3">
-        <v>0</v>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="S38" s="2">
+      <c r="S38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,47 +2397,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E41" s="3">
         <v>10600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>25300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2362,14 +2448,17 @@
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T41" s="3">
         <v>800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2401,13 +2490,13 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>10000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>4</v>
@@ -2418,47 +2507,50 @@
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E43" s="3">
         <v>7100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2474,47 +2566,50 @@
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>2500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1500</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
@@ -2530,29 +2625,32 @@
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E45" s="3">
         <v>9600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2568,15 +2666,15 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>4</v>
       </c>
@@ -2586,53 +2684,56 @@
       <c r="R45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E46" s="3">
         <v>30500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>32200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>46800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>30300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3600</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2642,14 +2743,17 @@
       <c r="R46" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T46" s="3">
         <v>1300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2692,49 +2796,52 @@
       <c r="P47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
       <c r="S47" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="T47" s="3">
         <v>172500</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>172500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E48" s="3">
         <v>1000</v>
       </c>
       <c r="F48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G48" s="3">
         <v>500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>300</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
@@ -2742,8 +2849,8 @@
       <c r="N48" s="3">
         <v>300</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
+      <c r="O48" s="3">
+        <v>300</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>4</v>
@@ -2754,53 +2861,56 @@
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E49" s="3">
         <v>26300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>31500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>26300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>26700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>26900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>26800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>26700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2800</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>4</v>
       </c>
@@ -2810,14 +2920,17 @@
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,16 +3044,19 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>400</v>
+      </c>
+      <c r="E52" s="3">
         <v>500</v>
-      </c>
-      <c r="E52" s="3">
-        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -2949,25 +3068,25 @@
         <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
       </c>
       <c r="K52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
@@ -2978,14 +3097,17 @@
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,47 +3162,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E54" s="3">
         <v>58800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>65500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>66200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>74900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>45100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>48600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>4</v>
       </c>
@@ -3090,14 +3215,17 @@
       <c r="R54" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T54" s="3">
         <v>173900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,47 +3269,48 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>4</v>
       </c>
@@ -3190,43 +3320,46 @@
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E58" s="3">
         <v>4900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>300</v>
-      </c>
-      <c r="L58" s="3">
-        <v>200</v>
       </c>
       <c r="M58" s="3">
         <v>200</v>
@@ -3234,14 +3367,14 @@
       <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
+      <c r="O58" s="3">
+        <v>200</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3252,46 +3385,49 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E59" s="3">
         <v>3600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
-      </c>
-      <c r="M59" s="3">
-        <v>100</v>
       </c>
       <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
+      <c r="O59" s="3">
+        <v>100</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
@@ -3302,53 +3438,56 @@
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3">
         <v>500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E60" s="3">
         <v>12000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10900</v>
-      </c>
-      <c r="F60" s="3">
-        <v>8600</v>
       </c>
       <c r="G60" s="3">
         <v>8600</v>
       </c>
       <c r="H60" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I60" s="3">
         <v>8400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2800</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>4</v>
       </c>
@@ -3358,25 +3497,28 @@
       <c r="R60" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E61" s="3">
         <v>28900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>28800</v>
-      </c>
-      <c r="F61" s="3">
-        <v>28600</v>
       </c>
       <c r="G61" s="3">
         <v>28600</v>
@@ -3385,26 +3527,26 @@
         <v>28600</v>
       </c>
       <c r="I61" s="3">
+        <v>28600</v>
+      </c>
+      <c r="J61" s="3">
         <v>18700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>37100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3420,41 +3562,44 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E62" s="3">
         <v>3000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18500</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
@@ -3470,14 +3615,17 @@
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T62" s="3">
         <v>12100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,47 +3798,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E66" s="3">
         <v>43900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>40100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>21700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>40200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>4</v>
       </c>
@@ -3694,14 +3851,17 @@
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T66" s="3">
         <v>12600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,47 +4116,50 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-156500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-144700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-132700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-124300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-119900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-99200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-86000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-74800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-62200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-56500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-36300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-15600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3996,14 +4169,17 @@
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T72" s="3">
         <v>-11200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-11100</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,47 +4352,50 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E76" s="3">
         <v>14900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-20100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>4</v>
       </c>
@@ -4220,14 +4405,17 @@
       <c r="R76" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T76" s="3">
         <v>161300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>161400</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="S80" s="2">
+      <c r="S80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12000</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G81" s="3">
         <v>-4400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13100</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K81" s="3">
         <v>-12600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S81" s="3">
-        <v>0</v>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,19 +4618,20 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
@@ -4448,37 +4646,40 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P83" s="3">
         <v>800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6100</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3">
         <v>-6400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10200</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
         <v>-6500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,8 +5054,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4861,27 +5081,27 @@
       <c r="J91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -4891,8 +5111,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3000</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>9400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-22500</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5119,8 +5352,8 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5137,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,64 +5547,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>40000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9100</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>18100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>20400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>9500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5399,8 +5647,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5417,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8500</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-8300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>30900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-7100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1900</v>
-      </c>
-      <c r="P102" s="3">
-        <v>-200</v>
       </c>
       <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="R102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSQH_QTR_FIN.xlsx
@@ -765,7 +765,7 @@
         <v>6700</v>
       </c>
       <c r="H8" s="3">
-        <v>7200</v>
+        <v>3500</v>
       </c>
       <c r="I8" s="3">
         <v>3200</v>
@@ -824,7 +824,7 @@
         <v>2800</v>
       </c>
       <c r="H9" s="3">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="I9" s="3">
         <v>100</v>
@@ -883,7 +883,7 @@
         <v>3900</v>
       </c>
       <c r="H10" s="3">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="I10" s="3">
         <v>3100</v>
@@ -965,7 +965,7 @@
         <v>1400</v>
       </c>
       <c r="H12" s="3">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="I12" s="3">
         <v>400</v>
@@ -1071,7 +1071,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>-500</v>
       </c>
       <c r="H14" s="3">
-        <v>-1800</v>
+        <v>500</v>
       </c>
       <c r="I14" s="3">
         <v>-200</v>
@@ -1142,7 +1142,7 @@
         <v>1200</v>
       </c>
       <c r="H15" s="3">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="I15" s="3">
         <v>700</v>
@@ -1209,7 +1209,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15100</v>
+        <v>14600</v>
       </c>
       <c r="E17" s="3">
         <v>14100</v>
@@ -1221,7 +1221,7 @@
         <v>18400</v>
       </c>
       <c r="H17" s="3">
-        <v>21600</v>
+        <v>12900</v>
       </c>
       <c r="I17" s="3">
         <v>13500</v>
@@ -1268,7 +1268,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-7700</v>
+        <v>-7300</v>
       </c>
       <c r="E18" s="3">
         <v>-9700</v>
@@ -1280,7 +1280,7 @@
         <v>-11700</v>
       </c>
       <c r="H18" s="3">
-        <v>-14400</v>
+        <v>-9400</v>
       </c>
       <c r="I18" s="3">
         <v>-10300</v>
@@ -1350,7 +1350,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2100</v>
+        <v>-1100</v>
       </c>
       <c r="E20" s="3">
         <v>-300</v>
@@ -1362,7 +1362,7 @@
         <v>-7400</v>
       </c>
       <c r="H20" s="3">
-        <v>7300</v>
+        <v>7600</v>
       </c>
       <c r="I20" s="3">
         <v>-2200</v>
@@ -1409,7 +1409,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3700</v>
+        <v>-4300</v>
       </c>
       <c r="E21" s="3">
         <v>-7700</v>
@@ -1421,7 +1421,7 @@
         <v>-3100</v>
       </c>
       <c r="H21" s="3">
-        <v>-20600</v>
+        <v>-16200</v>
       </c>
       <c r="I21" s="3">
         <v>-7400</v>
@@ -1539,7 +1539,7 @@
         <v>-4400</v>
       </c>
       <c r="H23" s="3">
-        <v>-20700</v>
+        <v>-18000</v>
       </c>
       <c r="I23" s="3">
         <v>-8700</v>
@@ -1716,7 +1716,7 @@
         <v>-4400</v>
       </c>
       <c r="H26" s="3">
-        <v>-20700</v>
+        <v>-18000</v>
       </c>
       <c r="I26" s="3">
         <v>-8600</v>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>-2700</v>
       </c>
       <c r="I29" s="3">
         <v>-4500</v>
@@ -2058,7 +2058,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2100</v>
+        <v>1100</v>
       </c>
       <c r="E32" s="3">
         <v>300</v>
@@ -2070,7 +2070,7 @@
         <v>7400</v>
       </c>
       <c r="H32" s="3">
-        <v>-7300</v>
+        <v>-7600</v>
       </c>
       <c r="I32" s="3">
         <v>2200</v>
@@ -2416,7 +2416,7 @@
         <v>28000</v>
       </c>
       <c r="H41" s="3">
-        <v>36300</v>
+        <v>35700</v>
       </c>
       <c r="I41" s="3">
         <v>4700</v>
@@ -2522,7 +2522,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9100</v>
+        <v>8200</v>
       </c>
       <c r="E43" s="3">
         <v>7100</v>
@@ -2534,7 +2534,7 @@
         <v>4600</v>
       </c>
       <c r="H43" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="I43" s="3">
         <v>4500</v>
@@ -2592,8 +2592,8 @@
       <c r="G44" s="3">
         <v>2400</v>
       </c>
-      <c r="H44" s="3">
-        <v>2700</v>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I44" s="3">
         <v>1500</v>
@@ -2640,7 +2640,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4400</v>
+        <v>5800</v>
       </c>
       <c r="E45" s="3">
         <v>9600</v>
@@ -2651,8 +2651,8 @@
       <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
+      <c r="H45" s="3">
+        <v>4000</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>4</v>
@@ -2888,7 +2888,7 @@
         <v>26300</v>
       </c>
       <c r="H49" s="3">
-        <v>26700</v>
+        <v>25600</v>
       </c>
       <c r="I49" s="3">
         <v>26900</v>
@@ -3065,7 +3065,7 @@
         <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
@@ -3288,7 +3288,7 @@
         <v>3100</v>
       </c>
       <c r="H57" s="3">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="I57" s="3">
         <v>3700</v>
@@ -3406,7 +3406,7 @@
         <v>100</v>
       </c>
       <c r="H59" s="3">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="I59" s="3">
         <v>600</v>
@@ -4625,7 +4625,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1100</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>700</v>
